--- a/reports/pdf_change_20260811.xlsx
+++ b/reports/pdf_change_20260811.xlsx
@@ -16,8 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="6">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="+#,##0;-#,##0;0"/>
+  </numFmts>
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,20 +38,37 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="007F7F7F"/>
+      <color rgb="001F3864"/>
       <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="001F3864"/>
-      <sz val="11"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00595959"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="000070C0"/>
     </font>
     <font>
       <i val="1"/>
       <color rgb="00808080"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -58,16 +77,36 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EDEDED"/>
+        <fgColor rgb="00DCE6F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DCE6F2"/>
+        <fgColor rgb="00C00000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000070C0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4E4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E4ECF6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDEDED"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -75,11 +114,25 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -90,10 +143,39 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -459,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -485,14 +567,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>캡처 1/7  ·  대기: KoAct, KoAct, TIME, TIME, PLUS, TIGER</t>
+          <t>캡처 6/7  ·  대기: TIGER</t>
         </is>
       </c>
     </row>
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,326억   ·   현금 132억(2.8%)      당일 2026-08-11  vs  전영업일 2026-08-10      매수 3종목  /  매도 6종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -506,127 +588,1437 @@
       <c r="J3" s="4" t="n"/>
       <c r="K3" s="4" t="n"/>
     </row>
-    <row r="5" ht="19" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="n"/>
-      <c r="F5" s="4" t="n"/>
-      <c r="G5" s="4" t="n"/>
-      <c r="H5" s="4" t="n"/>
-      <c r="I5" s="4" t="n"/>
-      <c r="J5" s="4" t="n"/>
-      <c r="K5" s="4" t="n"/>
-    </row>
-    <row r="7" ht="19" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n"/>
-      <c r="C7" s="4" t="n"/>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="4" t="n"/>
-      <c r="F7" s="4" t="n"/>
-      <c r="G7" s="4" t="n"/>
-      <c r="H7" s="4" t="n"/>
-      <c r="I7" s="4" t="n"/>
-      <c r="J7" s="4" t="n"/>
-      <c r="K7" s="4" t="n"/>
-    </row>
-    <row r="9" ht="19" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n"/>
-      <c r="C9" s="4" t="n"/>
-      <c r="D9" s="4" t="n"/>
-      <c r="E9" s="4" t="n"/>
-      <c r="F9" s="4" t="n"/>
-      <c r="G9" s="4" t="n"/>
-      <c r="H9" s="4" t="n"/>
-      <c r="I9" s="4" t="n"/>
-      <c r="J9" s="4" t="n"/>
-      <c r="K9" s="4" t="n"/>
-    </row>
-    <row r="11" ht="19" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="n"/>
-      <c r="C11" s="4" t="n"/>
-      <c r="D11" s="4" t="n"/>
-      <c r="E11" s="4" t="n"/>
-      <c r="F11" s="4" t="n"/>
-      <c r="G11" s="4" t="n"/>
-      <c r="H11" s="4" t="n"/>
-      <c r="I11" s="4" t="n"/>
-      <c r="J11" s="4" t="n"/>
-      <c r="K11" s="4" t="n"/>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="n"/>
+      <c r="I4" s="8" t="n"/>
+      <c r="J4" s="8" t="n"/>
+      <c r="K4" s="8" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>지엔씨에너지</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="C6" s="11" t="n">
+        <v>924528000</v>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>1.27%→1.38%</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>99→116</t>
+        </is>
+      </c>
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>덕산하이메탈</t>
+        </is>
+      </c>
+      <c r="H6" s="15" t="n">
+        <v>-92</v>
+      </c>
+      <c r="I6" s="15" t="n">
+        <v>-926752800</v>
+      </c>
+      <c r="J6" s="16" t="inlineStr">
+        <is>
+          <t>1.67%→1.42%</t>
+        </is>
+      </c>
+      <c r="K6" s="13" t="inlineStr">
+        <is>
+          <t>737→645</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>제주반도체</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="C7" s="11" t="n">
+        <v>1445296000</v>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>2.77%→3.27%</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>150→166</t>
+        </is>
+      </c>
+      <c r="G7" s="14" t="inlineStr">
+        <is>
+          <t>고영</t>
+        </is>
+      </c>
+      <c r="H7" s="15" t="n">
+        <v>-28</v>
+      </c>
+      <c r="I7" s="15" t="n">
+        <v>-914228000</v>
+      </c>
+      <c r="J7" s="16" t="inlineStr">
+        <is>
+          <t>1.02%→0.80%</t>
+        </is>
+      </c>
+      <c r="K7" s="13" t="inlineStr">
+        <is>
+          <t>140→112</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C8" s="11" t="n">
+        <v>1792200000</v>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>5.61%→6.25%</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>75→80</t>
+        </is>
+      </c>
+      <c r="G8" s="14" t="inlineStr">
+        <is>
+          <t>씨어스</t>
+        </is>
+      </c>
+      <c r="H8" s="15" t="n">
+        <v>-13</v>
+      </c>
+      <c r="I8" s="15" t="n">
+        <v>-331402500</v>
+      </c>
+      <c r="J8" s="16" t="inlineStr">
+        <is>
+          <t>0.28%→0.20%</t>
+        </is>
+      </c>
+      <c r="K8" s="13" t="inlineStr">
+        <is>
+          <t>49→36</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="17" t="n"/>
+      <c r="B9" s="17" t="n"/>
+      <c r="C9" s="17" t="n"/>
+      <c r="D9" s="17" t="n"/>
+      <c r="E9" s="17" t="n"/>
+      <c r="G9" s="14" t="inlineStr">
+        <is>
+          <t>주성엔지니어링</t>
+        </is>
+      </c>
+      <c r="H9" s="15" t="n">
+        <v>-12</v>
+      </c>
+      <c r="I9" s="15" t="n">
+        <v>-1789728000</v>
+      </c>
+      <c r="J9" s="16" t="inlineStr">
+        <is>
+          <t>0.78%→0.42%</t>
+        </is>
+      </c>
+      <c r="K9" s="13" t="inlineStr">
+        <is>
+          <t>25→13</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="17" t="n"/>
+      <c r="B10" s="17" t="n"/>
+      <c r="C10" s="17" t="n"/>
+      <c r="D10" s="17" t="n"/>
+      <c r="E10" s="17" t="n"/>
+      <c r="G10" s="14" t="inlineStr">
+        <is>
+          <t>원익IPS  (편출)</t>
+        </is>
+      </c>
+      <c r="H10" s="15" t="n">
+        <v>-9</v>
+      </c>
+      <c r="I10" s="15" t="n">
+        <v>-818541000</v>
+      </c>
+      <c r="J10" s="16" t="inlineStr">
+        <is>
+          <t>0.19%→0.00%</t>
+        </is>
+      </c>
+      <c r="K10" s="13" t="inlineStr">
+        <is>
+          <t>9→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="17" t="n"/>
+      <c r="B11" s="17" t="n"/>
+      <c r="C11" s="17" t="n"/>
+      <c r="D11" s="17" t="n"/>
+      <c r="E11" s="17" t="n"/>
+      <c r="G11" s="14" t="inlineStr">
+        <is>
+          <t>로보티즈</t>
+        </is>
+      </c>
+      <c r="H11" s="15" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I11" s="15" t="n">
+        <v>-763230000</v>
+      </c>
+      <c r="J11" s="16" t="inlineStr">
+        <is>
+          <t>3.26%→3.05%</t>
+        </is>
+      </c>
+      <c r="K11" s="13" t="inlineStr">
+        <is>
+          <t>58→55</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="19" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 557억   ·   현금 17억(3.0%)      당일 2026-08-11  vs  전영업일 2026-08-10      매수 0종목  /  매도 0종목</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="n"/>
-      <c r="C13" s="6" t="n"/>
-      <c r="D13" s="6" t="n"/>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="6" t="n"/>
-      <c r="H13" s="6" t="n"/>
-      <c r="I13" s="6" t="n"/>
-      <c r="J13" s="6" t="n"/>
-      <c r="K13" s="6" t="n"/>
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,897억   ·   현금 11억(0.2%)      당일 2026-08-11  vs  전영업일 2026-08-10      매수 7종목  /  매도 4종목</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n"/>
+      <c r="C13" s="4" t="n"/>
+      <c r="D13" s="4" t="n"/>
+      <c r="E13" s="4" t="n"/>
+      <c r="F13" s="4" t="n"/>
+      <c r="G13" s="4" t="n"/>
+      <c r="H13" s="4" t="n"/>
+      <c r="I13" s="4" t="n"/>
+      <c r="J13" s="4" t="n"/>
+      <c r="K13" s="4" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="n"/>
+      <c r="I14" s="8" t="n"/>
+      <c r="J14" s="8" t="n"/>
+      <c r="K14" s="8" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H15" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J15" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K15" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>큐라클</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="n">
+        <v>106</v>
+      </c>
+      <c r="C16" s="11" t="n">
+        <v>654825600</v>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>1.33%→1.59%</t>
+        </is>
+      </c>
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t>986→1,092</t>
+        </is>
+      </c>
+      <c r="G16" s="14" t="inlineStr">
+        <is>
+          <t>리가켐바이오</t>
+        </is>
+      </c>
+      <c r="H16" s="15" t="n">
+        <v>-33</v>
+      </c>
+      <c r="I16" s="15" t="n">
+        <v>-2089137600</v>
+      </c>
+      <c r="J16" s="16" t="inlineStr">
+        <is>
+          <t>5.60%→4.93%</t>
+        </is>
+      </c>
+      <c r="K16" s="13" t="inlineStr">
+        <is>
+          <t>363→330</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>앱클론</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="n">
+        <v>71</v>
+      </c>
+      <c r="C17" s="11" t="n">
+        <v>1300833600</v>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>2.07%→2.65%</t>
+        </is>
+      </c>
+      <c r="E17" s="13" t="inlineStr">
+        <is>
+          <t>542→613</t>
+        </is>
+      </c>
+      <c r="G17" s="14" t="inlineStr">
+        <is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="H17" s="15" t="n">
+        <v>-16</v>
+      </c>
+      <c r="I17" s="15" t="n">
+        <v>-2939904000</v>
+      </c>
+      <c r="J17" s="16" t="inlineStr">
+        <is>
+          <t>10.07%→9.80%</t>
+        </is>
+      </c>
+      <c r="K17" s="13" t="inlineStr">
+        <is>
+          <t>242→226</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>오스코텍</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="n">
+        <v>63</v>
+      </c>
+      <c r="C18" s="11" t="n">
+        <v>1264032000</v>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>3.11%→3.39%</t>
+        </is>
+      </c>
+      <c r="E18" s="13" t="inlineStr">
+        <is>
+          <t>652→715</t>
+        </is>
+      </c>
+      <c r="G18" s="14" t="inlineStr">
+        <is>
+          <t>셀트리온</t>
+        </is>
+      </c>
+      <c r="H18" s="15" t="n">
+        <v>-11</v>
+      </c>
+      <c r="I18" s="15" t="n">
+        <v>-1167408000</v>
+      </c>
+      <c r="J18" s="16" t="inlineStr">
+        <is>
+          <t>8.07%→7.17%</t>
+        </is>
+      </c>
+      <c r="K18" s="13" t="inlineStr">
+        <is>
+          <t>297→286</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>HLB이노베이션</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="n">
+        <v>61</v>
+      </c>
+      <c r="C19" s="11" t="n">
+        <v>433197600</v>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>1.71%→1.89%</t>
+        </is>
+      </c>
+      <c r="E19" s="13" t="inlineStr">
+        <is>
+          <t>1,066→1,127</t>
+        </is>
+      </c>
+      <c r="G19" s="14" t="inlineStr">
+        <is>
+          <t>한미약품</t>
+        </is>
+      </c>
+      <c r="H19" s="15" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I19" s="15" t="n">
+        <v>-1506120000</v>
+      </c>
+      <c r="J19" s="16" t="inlineStr">
+        <is>
+          <t>5.94%→5.28%</t>
+        </is>
+      </c>
+      <c r="K19" s="13" t="inlineStr">
+        <is>
+          <t>111→104</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>에이비엘바이오</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="n">
+        <v>42</v>
+      </c>
+      <c r="C20" s="11" t="n">
+        <v>2075673600</v>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>8.92%→9.30%</t>
+        </is>
+      </c>
+      <c r="E20" s="13" t="inlineStr">
+        <is>
+          <t>755→797</t>
+        </is>
+      </c>
+      <c r="G20" s="17" t="n"/>
+      <c r="H20" s="17" t="n"/>
+      <c r="I20" s="17" t="n"/>
+      <c r="J20" s="17" t="n"/>
+      <c r="K20" s="17" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>올릭스</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="n">
+        <v>29</v>
+      </c>
+      <c r="C21" s="11" t="n">
+        <v>2109993600</v>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>8.45%→9.28%</t>
+        </is>
+      </c>
+      <c r="E21" s="13" t="inlineStr">
+        <is>
+          <t>511→540</t>
+        </is>
+      </c>
+      <c r="G21" s="17" t="n"/>
+      <c r="H21" s="17" t="n"/>
+      <c r="I21" s="17" t="n"/>
+      <c r="J21" s="17" t="n"/>
+      <c r="K21" s="17" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>보로노이</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="C22" s="11" t="n">
+        <v>1210809600</v>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>2.16%→2.64%</t>
+        </is>
+      </c>
+      <c r="E22" s="13" t="inlineStr">
+        <is>
+          <t>107→120</t>
+        </is>
+      </c>
+      <c r="G22" s="17" t="n"/>
+      <c r="H22" s="17" t="n"/>
+      <c r="I22" s="17" t="n"/>
+      <c r="J22" s="17" t="n"/>
+      <c r="K22" s="17" t="n"/>
+    </row>
+    <row r="24" ht="19" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,466억   ·   현금 33억(1.2%)      당일 2026-08-11  vs  전영업일 2026-08-10      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="n"/>
+      <c r="C24" s="4" t="n"/>
+      <c r="D24" s="4" t="n"/>
+      <c r="E24" s="4" t="n"/>
+      <c r="F24" s="4" t="n"/>
+      <c r="G24" s="4" t="n"/>
+      <c r="H24" s="4" t="n"/>
+      <c r="I24" s="4" t="n"/>
+      <c r="J24" s="4" t="n"/>
+      <c r="K24" s="4" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="18" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="19" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
+    <row r="27" ht="19" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,281억   ·   현금 13억(0.5%)      당일 2026-08-11  vs  전영업일 2026-08-10      매수 3종목  /  매도 5종목</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="n"/>
+      <c r="C27" s="4" t="n"/>
+      <c r="D27" s="4" t="n"/>
+      <c r="E27" s="4" t="n"/>
+      <c r="F27" s="4" t="n"/>
+      <c r="G27" s="4" t="n"/>
+      <c r="H27" s="4" t="n"/>
+      <c r="I27" s="4" t="n"/>
+      <c r="J27" s="4" t="n"/>
+      <c r="K27" s="4" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="6" t="n"/>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H28" s="8" t="n"/>
+      <c r="I28" s="8" t="n"/>
+      <c r="J28" s="8" t="n"/>
+      <c r="K28" s="8" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G29" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H29" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I29" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J29" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K29" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>올릭스</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="n">
+        <v>106</v>
+      </c>
+      <c r="C30" s="11" t="n">
+        <v>4907884800</v>
+      </c>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>5.93%→8.27%</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>329→435</t>
+        </is>
+      </c>
+      <c r="G30" s="14" t="inlineStr">
+        <is>
+          <t>일동제약</t>
+        </is>
+      </c>
+      <c r="H30" s="15" t="n">
+        <v>-184</v>
+      </c>
+      <c r="I30" s="15" t="n">
+        <v>-982383360</v>
+      </c>
+      <c r="J30" s="16" t="inlineStr">
+        <is>
+          <t>0.91%→0.47%</t>
+        </is>
+      </c>
+      <c r="K30" s="13" t="inlineStr">
+        <is>
+          <t>400→216</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>오름테라퓨틱</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="n">
+        <v>105</v>
+      </c>
+      <c r="C31" s="11" t="n">
+        <v>2466072000</v>
+      </c>
+      <c r="D31" s="12" t="inlineStr">
+        <is>
+          <t>0.91%→1.97%</t>
+        </is>
+      </c>
+      <c r="E31" s="13" t="inlineStr">
+        <is>
+          <t>99→204</t>
+        </is>
+      </c>
+      <c r="G31" s="14" t="inlineStr">
+        <is>
+          <t>네이처셀</t>
+        </is>
+      </c>
+      <c r="H31" s="15" t="n">
+        <v>-160</v>
+      </c>
+      <c r="I31" s="15" t="n">
+        <v>-1231104000</v>
+      </c>
+      <c r="J31" s="16" t="inlineStr">
+        <is>
+          <t>0.67%→0.13%</t>
+        </is>
+      </c>
+      <c r="K31" s="13" t="inlineStr">
+        <is>
+          <t>202→42</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>보로노이</t>
+        </is>
+      </c>
+      <c r="B32" s="11" t="n">
+        <v>41</v>
+      </c>
+      <c r="C32" s="11" t="n">
+        <v>2430086400</v>
+      </c>
+      <c r="D32" s="12" t="inlineStr">
+        <is>
+          <t>1.32%→2.46%</t>
+        </is>
+      </c>
+      <c r="E32" s="13" t="inlineStr">
+        <is>
+          <t>60→101</t>
+        </is>
+      </c>
+      <c r="G32" s="14" t="inlineStr">
+        <is>
+          <t>HK이노엔  (편출)</t>
+        </is>
+      </c>
+      <c r="H32" s="15" t="n">
+        <v>-102</v>
+      </c>
+      <c r="I32" s="15" t="n">
+        <v>-1425715200</v>
+      </c>
+      <c r="J32" s="16" t="inlineStr">
+        <is>
+          <t>0.63%→0.00%</t>
+        </is>
+      </c>
+      <c r="K32" s="13" t="inlineStr">
+        <is>
+          <t>102→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="17" t="n"/>
+      <c r="B33" s="17" t="n"/>
+      <c r="C33" s="17" t="n"/>
+      <c r="D33" s="17" t="n"/>
+      <c r="E33" s="17" t="n"/>
+      <c r="G33" s="14" t="inlineStr">
+        <is>
+          <t>셀트리온</t>
+        </is>
+      </c>
+      <c r="H33" s="15" t="n">
+        <v>-72</v>
+      </c>
+      <c r="I33" s="15" t="n">
+        <v>-4862592000</v>
+      </c>
+      <c r="J33" s="16" t="inlineStr">
+        <is>
+          <t>11.00%→8.29%</t>
+        </is>
+      </c>
+      <c r="K33" s="13" t="inlineStr">
+        <is>
+          <t>371→299</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="17" t="n"/>
+      <c r="B34" s="17" t="n"/>
+      <c r="C34" s="17" t="n"/>
+      <c r="D34" s="17" t="n"/>
+      <c r="E34" s="17" t="n"/>
+      <c r="G34" s="14" t="inlineStr">
+        <is>
+          <t>펩트론  (편출)</t>
+        </is>
+      </c>
+      <c r="H34" s="15" t="n">
+        <v>-20</v>
+      </c>
+      <c r="I34" s="15" t="n">
+        <v>-1221696000</v>
+      </c>
+      <c r="J34" s="16" t="inlineStr">
+        <is>
+          <t>0.54%→0.00%</t>
+        </is>
+      </c>
+      <c r="K34" s="13" t="inlineStr">
+        <is>
+          <t>20→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="19" customHeight="1">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 264억   ·   현금 7억(2.6%)      당일 2026-08-11  vs  전영업일 2026-08-10      매수 3종목  /  매도 3종목</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="n"/>
+      <c r="C36" s="4" t="n"/>
+      <c r="D36" s="4" t="n"/>
+      <c r="E36" s="4" t="n"/>
+      <c r="F36" s="4" t="n"/>
+      <c r="G36" s="4" t="n"/>
+      <c r="H36" s="4" t="n"/>
+      <c r="I36" s="4" t="n"/>
+      <c r="J36" s="4" t="n"/>
+      <c r="K36" s="4" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="n"/>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="n"/>
+      <c r="E37" s="6" t="n"/>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H37" s="8" t="n"/>
+      <c r="I37" s="8" t="n"/>
+      <c r="J37" s="8" t="n"/>
+      <c r="K37" s="8" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G38" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H38" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I38" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J38" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K38" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>씨어스</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="C39" s="11" t="n">
+        <v>69920000</v>
+      </c>
+      <c r="D39" s="12" t="inlineStr">
+        <is>
+          <t>6.67%→6.93%</t>
+        </is>
+      </c>
+      <c r="E39" s="13" t="inlineStr">
+        <is>
+          <t>980→1,020</t>
+        </is>
+      </c>
+      <c r="G39" s="14" t="inlineStr">
+        <is>
+          <t>금양그린파워</t>
+        </is>
+      </c>
+      <c r="H39" s="15" t="n">
+        <v>-53</v>
+      </c>
+      <c r="I39" s="15" t="n">
+        <v>-31539240</v>
+      </c>
+      <c r="J39" s="16" t="inlineStr">
+        <is>
+          <t>0.87%→0.75%</t>
+        </is>
+      </c>
+      <c r="K39" s="13" t="inlineStr">
+        <is>
+          <t>375→322</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>노바렉스  (신규)</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="C40" s="11" t="n">
+        <v>27203440</v>
+      </c>
+      <c r="D40" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→0.11%</t>
+        </is>
+      </c>
+      <c r="E40" s="13" t="inlineStr">
+        <is>
+          <t>0→22</t>
+        </is>
+      </c>
+      <c r="G40" s="14" t="inlineStr">
+        <is>
+          <t>상아프론테크</t>
+        </is>
+      </c>
+      <c r="H40" s="15" t="n">
+        <v>-29</v>
+      </c>
+      <c r="I40" s="15" t="n">
+        <v>-29908280</v>
+      </c>
+      <c r="J40" s="16" t="inlineStr">
+        <is>
+          <t>0.43%→0.31%</t>
+        </is>
+      </c>
+      <c r="K40" s="13" t="inlineStr">
+        <is>
+          <t>107→78</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="10" t="inlineStr">
+        <is>
+          <t>코스맥스엔비티  (신규)</t>
+        </is>
+      </c>
+      <c r="B41" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="C41" s="11" t="n">
+        <v>11149960</v>
+      </c>
+      <c r="D41" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→0.04%</t>
+        </is>
+      </c>
+      <c r="E41" s="13" t="inlineStr">
+        <is>
+          <t>0→17</t>
+        </is>
+      </c>
+      <c r="G41" s="14" t="inlineStr">
+        <is>
+          <t>상신이디피</t>
+        </is>
+      </c>
+      <c r="H41" s="15" t="n">
+        <v>-27</v>
+      </c>
+      <c r="I41" s="15" t="n">
+        <v>-32503680</v>
+      </c>
+      <c r="J41" s="16" t="inlineStr">
+        <is>
+          <t>1.63%→1.51%</t>
+        </is>
+      </c>
+      <c r="K41" s="13" t="inlineStr">
+        <is>
+          <t>349→322</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="19" customHeight="1">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 557억   ·   현금 10억(1.6%)      당일 2026-08-11  vs  전영업일 2026-08-10      매수 4종목  /  매도 2종목</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="n"/>
+      <c r="C43" s="4" t="n"/>
+      <c r="D43" s="4" t="n"/>
+      <c r="E43" s="4" t="n"/>
+      <c r="F43" s="4" t="n"/>
+      <c r="G43" s="4" t="n"/>
+      <c r="H43" s="4" t="n"/>
+      <c r="I43" s="4" t="n"/>
+      <c r="J43" s="4" t="n"/>
+      <c r="K43" s="4" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="n"/>
+      <c r="C44" s="6" t="n"/>
+      <c r="D44" s="6" t="n"/>
+      <c r="E44" s="6" t="n"/>
+      <c r="G44" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H44" s="8" t="n"/>
+      <c r="I44" s="8" t="n"/>
+      <c r="J44" s="8" t="n"/>
+      <c r="K44" s="8" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E45" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G45" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H45" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I45" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J45" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K45" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="10" t="inlineStr">
+        <is>
+          <t>알지노믹스</t>
+        </is>
+      </c>
+      <c r="B46" s="11" t="n">
+        <v>130</v>
+      </c>
+      <c r="C46" s="11" t="n">
+        <v>551655000</v>
+      </c>
+      <c r="D46" s="12" t="inlineStr">
+        <is>
+          <t>2.56%→3.58%</t>
+        </is>
+      </c>
+      <c r="E46" s="13" t="inlineStr">
+        <is>
+          <t>368→498</t>
+        </is>
+      </c>
+      <c r="G46" s="14" t="inlineStr">
+        <is>
+          <t>휴젤</t>
+        </is>
+      </c>
+      <c r="H46" s="15" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I46" s="15" t="n">
+        <v>-803562500</v>
+      </c>
+      <c r="J46" s="16" t="inlineStr">
+        <is>
+          <t>5.40%→3.65%</t>
+        </is>
+      </c>
+      <c r="K46" s="13" t="inlineStr">
+        <is>
+          <t>92→67</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="10" t="inlineStr">
+        <is>
+          <t>오름테라퓨틱</t>
+        </is>
+      </c>
+      <c r="B47" s="11" t="n">
+        <v>76</v>
+      </c>
+      <c r="C47" s="11" t="n">
+        <v>610926000</v>
+      </c>
+      <c r="D47" s="12" t="inlineStr">
+        <is>
+          <t>1.37%→2.44%</t>
+        </is>
+      </c>
+      <c r="E47" s="13" t="inlineStr">
+        <is>
+          <t>103→179</t>
+        </is>
+      </c>
+      <c r="G47" s="14" t="inlineStr">
+        <is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="H47" s="15" t="n">
+        <v>-11</v>
+      </c>
+      <c r="I47" s="15" t="n">
+        <v>-440220000</v>
+      </c>
+      <c r="J47" s="16" t="inlineStr">
+        <is>
+          <t>9.81%→9.42%</t>
+        </is>
+      </c>
+      <c r="K47" s="13" t="inlineStr">
+        <is>
+          <t>150→139</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="10" t="inlineStr">
+        <is>
+          <t>앱클론</t>
+        </is>
+      </c>
+      <c r="B48" s="11" t="n">
+        <v>55</v>
+      </c>
+      <c r="C48" s="11" t="n">
+        <v>219477500</v>
+      </c>
+      <c r="D48" s="12" t="inlineStr">
+        <is>
+          <t>3.36%→4.15%</t>
+        </is>
+      </c>
+      <c r="E48" s="13" t="inlineStr">
+        <is>
+          <t>559→614</t>
+        </is>
+      </c>
+      <c r="G48" s="17" t="n"/>
+      <c r="H48" s="17" t="n"/>
+      <c r="I48" s="17" t="n"/>
+      <c r="J48" s="17" t="n"/>
+      <c r="K48" s="17" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="10" t="inlineStr">
+        <is>
+          <t>보로노이</t>
+        </is>
+      </c>
+      <c r="B49" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="C49" s="11" t="n">
+        <v>547722000</v>
+      </c>
+      <c r="D49" s="12" t="inlineStr">
+        <is>
+          <t>1.96%→3.06%</t>
+        </is>
+      </c>
+      <c r="E49" s="13" t="inlineStr">
+        <is>
+          <t>62→89</t>
+        </is>
+      </c>
+      <c r="G49" s="17" t="n"/>
+      <c r="H49" s="17" t="n"/>
+      <c r="I49" s="17" t="n"/>
+      <c r="J49" s="17" t="n"/>
+      <c r="K49" s="17" t="n"/>
+    </row>
+    <row r="51" ht="19" customHeight="1">
+      <c r="A51" s="19" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B16" s="4" t="n"/>
-      <c r="C16" s="4" t="n"/>
-      <c r="D16" s="4" t="n"/>
-      <c r="E16" s="4" t="n"/>
-      <c r="F16" s="4" t="n"/>
-      <c r="G16" s="4" t="n"/>
-      <c r="H16" s="4" t="n"/>
-      <c r="I16" s="4" t="n"/>
-      <c r="J16" s="4" t="n"/>
-      <c r="K16" s="4" t="n"/>
+      <c r="B51" s="20" t="n"/>
+      <c r="C51" s="20" t="n"/>
+      <c r="D51" s="20" t="n"/>
+      <c r="E51" s="20" t="n"/>
+      <c r="F51" s="20" t="n"/>
+      <c r="G51" s="20" t="n"/>
+      <c r="H51" s="20" t="n"/>
+      <c r="I51" s="20" t="n"/>
+      <c r="J51" s="20" t="n"/>
+      <c r="K51" s="20" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="20">
+    <mergeCell ref="A24:K24"/>
+    <mergeCell ref="A51:K51"/>
+    <mergeCell ref="A36:K36"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A25:K25"/>
+    <mergeCell ref="G28:K28"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="G37:K37"/>
+    <mergeCell ref="A27:K27"/>
     <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A7:K7"/>
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A11:K11"/>
-    <mergeCell ref="A16:K16"/>
-    <mergeCell ref="A5:K5"/>
+    <mergeCell ref="G14:K14"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="G4:K4"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A43:K43"/>
+    <mergeCell ref="G44:K44"/>
     <mergeCell ref="A13:K13"/>
-    <mergeCell ref="A14:K14"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A9:K9"/>
+    <mergeCell ref="A44:E44"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/pdf_change_20260811.xlsx
+++ b/reports/pdf_change_20260811.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,326억   ·   현금 132억(2.8%)      당일 2026-08-11  vs  전영업일 2026-08-10      매수 3종목  /  매도 6종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,738억   ·   현금 133억(2.8%)      당일 2026-08-11  vs  전영업일 2026-08-10      매수 3종목  /  매도 6종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,7 +670,7 @@
         <v>17</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>924528000</v>
+        <v>926323200</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>-92</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-926752800</v>
+        <v>-928552320</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>16</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>1445296000</v>
+        <v>1448102400</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>-28</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-914228000</v>
+        <v>-916003200</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>5</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>1792200000</v>
+        <v>1795680000</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>-13</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-331402500</v>
+        <v>-332046000</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>-12</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-1789728000</v>
+        <v>-1793203200</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>-9</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-818541000</v>
+        <v>-820130400</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
         <v>-3</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-763230000</v>
+        <v>-764712000</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
     <row r="13" ht="19" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,897억   ·   현금 11억(0.2%)      당일 2026-08-11  vs  전영업일 2026-08-10      매수 7종목  /  매도 4종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,270억   ·   현금 11억(0.2%)      당일 2026-08-11  vs  전영업일 2026-08-10      매수 7종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B13" s="4" t="n"/>
@@ -1228,7 +1228,7 @@
     <row r="24" ht="19" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,466억   ·   현금 33억(1.2%)      당일 2026-08-11  vs  전영업일 2026-08-10      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,676억   ·   현금 33억(1.2%)      당일 2026-08-11  vs  전영업일 2026-08-10      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B24" s="4" t="n"/>
@@ -1252,7 +1252,7 @@
     <row r="27" ht="19" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,281억   ·   현금 13억(0.5%)      당일 2026-08-11  vs  전영업일 2026-08-10      매수 3종목  /  매도 5종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,463억   ·   현금 13억(0.5%)      당일 2026-08-11  vs  전영업일 2026-08-10      매수 3종목  /  매도 5종목</t>
         </is>
       </c>
       <c r="B27" s="4" t="n"/>
@@ -1348,7 +1348,7 @@
         <v>106</v>
       </c>
       <c r="C30" s="11" t="n">
-        <v>4907884800</v>
+        <v>4922491600</v>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>-184</v>
       </c>
       <c r="I30" s="15" t="n">
-        <v>-982383360</v>
+        <v>-985307120</v>
       </c>
       <c r="J30" s="16" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>105</v>
       </c>
       <c r="C31" s="11" t="n">
-        <v>2466072000</v>
+        <v>2473411500</v>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>-160</v>
       </c>
       <c r="I31" s="15" t="n">
-        <v>-1231104000</v>
+        <v>-1234768000</v>
       </c>
       <c r="J31" s="16" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         <v>41</v>
       </c>
       <c r="C32" s="11" t="n">
-        <v>2430086400</v>
+        <v>2437318800</v>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>-102</v>
       </c>
       <c r="I32" s="15" t="n">
-        <v>-1425715200</v>
+        <v>-1429958400</v>
       </c>
       <c r="J32" s="16" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>-72</v>
       </c>
       <c r="I33" s="15" t="n">
-        <v>-4862592000</v>
+        <v>-4877064000</v>
       </c>
       <c r="J33" s="16" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         <v>-20</v>
       </c>
       <c r="I34" s="15" t="n">
-        <v>-1221696000</v>
+        <v>-1225332000</v>
       </c>
       <c r="J34" s="16" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
     <row r="36" ht="19" customHeight="1">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 264억   ·   현금 7억(2.6%)      당일 2026-08-11  vs  전영업일 2026-08-10      매수 3종목  /  매도 3종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 287억   ·   현금 7억(2.4%)      당일 2026-08-11  vs  전영업일 2026-08-10      매수 3종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B36" s="4" t="n"/>
@@ -1625,11 +1625,11 @@
         <v>40</v>
       </c>
       <c r="C39" s="11" t="n">
-        <v>69920000</v>
+        <v>75240000</v>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>6.67%→6.93%</t>
+          <t>6.58%→6.84%</t>
         </is>
       </c>
       <c r="E39" s="13" t="inlineStr">
@@ -1646,11 +1646,11 @@
         <v>-53</v>
       </c>
       <c r="I39" s="15" t="n">
-        <v>-31539240</v>
+        <v>-32425400</v>
       </c>
       <c r="J39" s="16" t="inlineStr">
         <is>
-          <t>0.87%→0.75%</t>
+          <t>0.82%→0.70%</t>
         </is>
       </c>
       <c r="K39" s="13" t="inlineStr">
@@ -1669,11 +1669,11 @@
         <v>22</v>
       </c>
       <c r="C40" s="11" t="n">
-        <v>27203440</v>
+        <v>28089600</v>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.11%</t>
+          <t>0.00%→0.10%</t>
         </is>
       </c>
       <c r="E40" s="13" t="inlineStr">
@@ -1690,11 +1690,11 @@
         <v>-29</v>
       </c>
       <c r="I40" s="15" t="n">
-        <v>-29908280</v>
+        <v>-31869840</v>
       </c>
       <c r="J40" s="16" t="inlineStr">
         <is>
-          <t>0.43%→0.31%</t>
+          <t>0.42%→0.31%</t>
         </is>
       </c>
       <c r="K40" s="13" t="inlineStr">
@@ -1713,11 +1713,11 @@
         <v>17</v>
       </c>
       <c r="C41" s="11" t="n">
-        <v>11149960</v>
+        <v>13824400</v>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.04%</t>
+          <t>0.00%→0.05%</t>
         </is>
       </c>
       <c r="E41" s="13" t="inlineStr">
@@ -1734,11 +1734,11 @@
         <v>-27</v>
       </c>
       <c r="I41" s="15" t="n">
-        <v>-32503680</v>
+        <v>-36689760</v>
       </c>
       <c r="J41" s="16" t="inlineStr">
         <is>
-          <t>1.63%→1.51%</t>
+          <t>1.69%→1.56%</t>
         </is>
       </c>
       <c r="K41" s="13" t="inlineStr">
@@ -1750,7 +1750,7 @@
     <row r="43" ht="19" customHeight="1">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 557억   ·   현금 10억(1.6%)      당일 2026-08-11  vs  전영업일 2026-08-10      매수 4종목  /  매도 2종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 621억   ·   현금 10억(1.6%)      당일 2026-08-11  vs  전영업일 2026-08-10      매수 4종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B43" s="4" t="n"/>
@@ -1846,7 +1846,7 @@
         <v>130</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>551655000</v>
+        <v>556452000</v>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>-25</v>
       </c>
       <c r="I46" s="15" t="n">
-        <v>-803562500</v>
+        <v>-810550000</v>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>76</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>610926000</v>
+        <v>616238400</v>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>-11</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-440220000</v>
+        <v>-444048000</v>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>55</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>219477500</v>
+        <v>221386000</v>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>27</v>
       </c>
       <c r="C49" s="11" t="n">
-        <v>547722000</v>
+        <v>552484800</v>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
